--- a/JSYD.xlsx
+++ b/JSYD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\zb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{349950F1-74F5-4278-9B67-B4ADC263A060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBB213A-5A4E-45B8-9BC1-228FDE916503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12520" uniqueCount="3821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12520" uniqueCount="3822">
   <si>
     <t>频道名称</t>
   </si>
@@ -11517,10 +11517,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CCTV中视购物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无锡新闻综合</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11534,6 +11530,14 @@
   </si>
   <si>
     <t>茶频道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLTV_3221228855</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLTV_3221228852</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20327,7 +20331,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="B420" t="s">
         <v>2916</v>
@@ -20347,7 +20351,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B421" t="s">
         <v>2932</v>
@@ -24167,7 +24171,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>3816</v>
+        <v>3821</v>
       </c>
       <c r="B612" t="s">
         <v>2915</v>
@@ -24187,7 +24191,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>3803</v>
+        <v>3820</v>
       </c>
       <c r="B613" t="s">
         <v>2917</v>
@@ -24247,7 +24251,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="B616" t="s">
         <v>2919</v>
@@ -24427,7 +24431,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="B625" t="s">
         <v>2934</v>
@@ -24650,8 +24654,8 @@
     <sortCondition ref="B2:B626"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A494:A1048576 A1:A490">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="A1:A490 A494:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50025,7 +50029,7 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -61750,7 +61754,7 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -73475,7 +73479,7 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/JSYD.xlsx
+++ b/JSYD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\zb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2623CA68-4184-4206-B33A-C7706889EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEACD76-A7AB-4D66-896B-23775953452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11369,9 +11369,6 @@
     <t>咪视界4K</t>
   </si>
   <si>
-    <t>苏州4K</t>
-  </si>
-  <si>
     <t>http://gslbserv.itv.cmvideo.cn/3000000010000015686/index.m3u8?channel-id=FifastbLive&amp;Contentid=3000000010000015686&amp;livemode=1&amp;stbId=3</t>
   </si>
   <si>
@@ -11436,16 +11433,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4K测试-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4K测试-2</t>
-  </si>
-  <si>
-    <t>4K测试-3</t>
-  </si>
-  <si>
     <t>无锡新闻综合</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11767,6 +11754,22 @@
   </si>
   <si>
     <t>8920</t>
+  </si>
+  <si>
+    <t>苏州4K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8740</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8589</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8873</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11820,8 +11823,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -12170,7 +12174,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19302,7 +19306,7 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>3798</v>
+        <v>3794</v>
       </c>
       <c r="B420" t="s">
         <v>2915</v>
@@ -19319,7 +19323,7 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>3799</v>
+        <v>3795</v>
       </c>
       <c r="B421" t="s">
         <v>2931</v>
@@ -20512,7 +20516,7 @@
         <v>3771</v>
       </c>
       <c r="B491" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="C491" t="s">
         <v>3438</v>
@@ -20529,7 +20533,7 @@
         <v>3772</v>
       </c>
       <c r="B492" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="C492" t="s">
         <v>3438</v>
@@ -20543,10 +20547,10 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>3773</v>
+        <v>3901</v>
       </c>
       <c r="B493" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="C493" t="s">
         <v>3438</v>
@@ -20559,28 +20563,28 @@
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
-        <v>3795</v>
+      <c r="A494" s="1" t="s">
+        <v>3902</v>
       </c>
       <c r="B494" t="s">
-        <v>2767</v>
+        <v>2868</v>
       </c>
       <c r="C494" t="s">
         <v>3438</v>
       </c>
       <c r="E494" t="s">
-        <v>240</v>
+        <v>3670</v>
       </c>
       <c r="F494" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
-        <v>3796</v>
+      <c r="A495" s="1" t="s">
+        <v>3903</v>
       </c>
       <c r="B495" t="s">
-        <v>2921</v>
+        <v>2767</v>
       </c>
       <c r="C495" t="s">
         <v>3438</v>
@@ -20593,17 +20597,17 @@
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
-        <v>3797</v>
+      <c r="A496" s="1" t="s">
+        <v>3904</v>
       </c>
       <c r="B496" t="s">
-        <v>2868</v>
+        <v>2921</v>
       </c>
       <c r="C496" t="s">
         <v>3438</v>
       </c>
       <c r="E496" t="s">
-        <v>3670</v>
+        <v>240</v>
       </c>
       <c r="F496" t="s">
         <v>11</v>
@@ -20696,13 +20700,13 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>3640</v>
+        <v>3878</v>
       </c>
       <c r="B502" t="s">
-        <v>2748</v>
+        <v>2911</v>
       </c>
       <c r="C502" t="s">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="E502" t="s">
         <v>10</v>
@@ -20713,10 +20717,10 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>3533</v>
+        <v>3640</v>
       </c>
       <c r="B503" t="s">
-        <v>2363</v>
+        <v>2748</v>
       </c>
       <c r="C503" t="s">
         <v>3683</v>
@@ -20730,10 +20734,10 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>3563</v>
+        <v>3533</v>
       </c>
       <c r="B504" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="C504" t="s">
         <v>3683</v>
@@ -20747,10 +20751,10 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="B505" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="C505" t="s">
         <v>3683</v>
@@ -20767,7 +20771,7 @@
         <v>3562</v>
       </c>
       <c r="B506" t="s">
-        <v>2478</v>
+        <v>2370</v>
       </c>
       <c r="C506" t="s">
         <v>3683</v>
@@ -20781,16 +20785,16 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>3547</v>
+        <v>3562</v>
       </c>
       <c r="B507" t="s">
-        <v>2732</v>
+        <v>2478</v>
       </c>
       <c r="C507" t="s">
         <v>3683</v>
       </c>
       <c r="E507" t="s">
-        <v>786</v>
+        <v>10</v>
       </c>
       <c r="F507" t="s">
         <v>11</v>
@@ -20798,16 +20802,16 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>3534</v>
+        <v>3547</v>
       </c>
       <c r="B508" t="s">
-        <v>2803</v>
+        <v>2732</v>
       </c>
       <c r="C508" t="s">
         <v>3683</v>
       </c>
       <c r="E508" t="s">
-        <v>10</v>
+        <v>786</v>
       </c>
       <c r="F508" t="s">
         <v>11</v>
@@ -20815,10 +20819,10 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>3539</v>
+        <v>3534</v>
       </c>
       <c r="B509" t="s">
-        <v>2741</v>
+        <v>2803</v>
       </c>
       <c r="C509" t="s">
         <v>3683</v>
@@ -20832,10 +20836,10 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B510" t="s">
-        <v>2753</v>
+        <v>2741</v>
       </c>
       <c r="C510" t="s">
         <v>3683</v>
@@ -20849,10 +20853,10 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B511" t="s">
-        <v>2738</v>
+        <v>2753</v>
       </c>
       <c r="C511" t="s">
         <v>3683</v>
@@ -20866,10 +20870,10 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="B512" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="C512" t="s">
         <v>3683</v>
@@ -20883,10 +20887,10 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="B513" t="s">
-        <v>2754</v>
+        <v>2739</v>
       </c>
       <c r="C513" t="s">
         <v>3683</v>
@@ -20900,10 +20904,10 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="B514" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
       <c r="C514" t="s">
         <v>3683</v>
@@ -20917,10 +20921,10 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="B515" t="s">
-        <v>2774</v>
+        <v>2762</v>
       </c>
       <c r="C515" t="s">
         <v>3683</v>
@@ -20934,10 +20938,10 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>3570</v>
+        <v>3545</v>
       </c>
       <c r="B516" t="s">
-        <v>2757</v>
+        <v>2774</v>
       </c>
       <c r="C516" t="s">
         <v>3683</v>
@@ -20951,10 +20955,10 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="B517" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="C517" t="s">
         <v>3683</v>
@@ -20968,10 +20972,10 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="B518" t="s">
-        <v>2766</v>
+        <v>2758</v>
       </c>
       <c r="C518" t="s">
         <v>3683</v>
@@ -20985,10 +20989,10 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>3575</v>
+        <v>3572</v>
       </c>
       <c r="B519" t="s">
-        <v>2737</v>
+        <v>2766</v>
       </c>
       <c r="C519" t="s">
         <v>3683</v>
@@ -21002,10 +21006,10 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>3620</v>
+        <v>3575</v>
       </c>
       <c r="B520" t="s">
-        <v>2765</v>
+        <v>2737</v>
       </c>
       <c r="C520" t="s">
         <v>3683</v>
@@ -21019,10 +21023,10 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>3647</v>
+        <v>3620</v>
       </c>
       <c r="B521" t="s">
-        <v>2825</v>
+        <v>2765</v>
       </c>
       <c r="C521" t="s">
         <v>3683</v>
@@ -21036,13 +21040,13 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>3802</v>
+        <v>3647</v>
       </c>
       <c r="B522" t="s">
-        <v>2374</v>
+        <v>2825</v>
       </c>
       <c r="C522" t="s">
-        <v>9</v>
+        <v>3683</v>
       </c>
       <c r="E522" t="s">
         <v>10</v>
@@ -21053,10 +21057,10 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>3803</v>
+        <v>3798</v>
       </c>
       <c r="B523" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="C523" t="s">
         <v>9</v>
@@ -21070,10 +21074,10 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>3804</v>
+        <v>3799</v>
       </c>
       <c r="B524" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="C524" t="s">
         <v>9</v>
@@ -21087,10 +21091,10 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>3805</v>
+        <v>3800</v>
       </c>
       <c r="B525" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="C525" t="s">
         <v>9</v>
@@ -21104,10 +21108,10 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>3806</v>
+        <v>3801</v>
       </c>
       <c r="B526" t="s">
-        <v>2389</v>
+        <v>2381</v>
       </c>
       <c r="C526" t="s">
         <v>9</v>
@@ -21121,10 +21125,10 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>3807</v>
+        <v>3802</v>
       </c>
       <c r="B527" t="s">
-        <v>2505</v>
+        <v>2389</v>
       </c>
       <c r="C527" t="s">
         <v>9</v>
@@ -21138,10 +21142,10 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>3808</v>
+        <v>3803</v>
       </c>
       <c r="B528" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="C528" t="s">
         <v>9</v>
@@ -21155,10 +21159,10 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>3809</v>
+        <v>3804</v>
       </c>
       <c r="B529" t="s">
-        <v>2596</v>
+        <v>2507</v>
       </c>
       <c r="C529" t="s">
         <v>9</v>
@@ -21172,16 +21176,16 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>3810</v>
+        <v>3805</v>
       </c>
       <c r="B530" t="s">
-        <v>2612</v>
+        <v>2596</v>
       </c>
       <c r="C530" t="s">
         <v>9</v>
       </c>
       <c r="E530" t="s">
-        <v>311</v>
+        <v>10</v>
       </c>
       <c r="F530" t="s">
         <v>11</v>
@@ -21189,16 +21193,16 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>3811</v>
+        <v>3806</v>
       </c>
       <c r="B531" t="s">
-        <v>2618</v>
+        <v>2612</v>
       </c>
       <c r="C531" t="s">
         <v>9</v>
       </c>
       <c r="E531" t="s">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="F531" t="s">
         <v>11</v>
@@ -21206,10 +21210,10 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>3812</v>
+        <v>3807</v>
       </c>
       <c r="B532" t="s">
-        <v>2622</v>
+        <v>2618</v>
       </c>
       <c r="C532" t="s">
         <v>9</v>
@@ -21223,10 +21227,10 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>3813</v>
+        <v>3808</v>
       </c>
       <c r="B533" t="s">
-        <v>2649</v>
+        <v>2622</v>
       </c>
       <c r="C533" t="s">
         <v>9</v>
@@ -21240,10 +21244,10 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>3814</v>
+        <v>3809</v>
       </c>
       <c r="B534" t="s">
-        <v>2669</v>
+        <v>2649</v>
       </c>
       <c r="C534" t="s">
         <v>9</v>
@@ -21257,10 +21261,10 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>3815</v>
+        <v>3810</v>
       </c>
       <c r="B535" t="s">
-        <v>2677</v>
+        <v>2669</v>
       </c>
       <c r="C535" t="s">
         <v>9</v>
@@ -21274,10 +21278,10 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>3816</v>
+        <v>3811</v>
       </c>
       <c r="B536" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="C536" t="s">
         <v>9</v>
@@ -21291,10 +21295,10 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>3817</v>
+        <v>3812</v>
       </c>
       <c r="B537" t="s">
-        <v>2719</v>
+        <v>2685</v>
       </c>
       <c r="C537" t="s">
         <v>9</v>
@@ -21308,10 +21312,10 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>3818</v>
+        <v>3813</v>
       </c>
       <c r="B538" t="s">
-        <v>2742</v>
+        <v>2719</v>
       </c>
       <c r="C538" t="s">
         <v>9</v>
@@ -21325,10 +21329,10 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>3819</v>
+        <v>3814</v>
       </c>
       <c r="B539" t="s">
-        <v>2761</v>
+        <v>2742</v>
       </c>
       <c r="C539" t="s">
         <v>9</v>
@@ -21342,10 +21346,10 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>3820</v>
+        <v>3815</v>
       </c>
       <c r="B540" t="s">
-        <v>2768</v>
+        <v>2761</v>
       </c>
       <c r="C540" t="s">
         <v>9</v>
@@ -21359,10 +21363,10 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>3821</v>
+        <v>3816</v>
       </c>
       <c r="B541" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="C541" t="s">
         <v>9</v>
@@ -21376,10 +21380,10 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>3822</v>
+        <v>3817</v>
       </c>
       <c r="B542" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="C542" t="s">
         <v>9</v>
@@ -21393,10 +21397,10 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>3823</v>
+        <v>3818</v>
       </c>
       <c r="B543" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="C543" t="s">
         <v>9</v>
@@ -21410,10 +21414,10 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>3824</v>
+        <v>3819</v>
       </c>
       <c r="B544" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="C544" t="s">
         <v>9</v>
@@ -21427,10 +21431,10 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>3825</v>
+        <v>3820</v>
       </c>
       <c r="B545" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C545" t="s">
         <v>9</v>
@@ -21444,10 +21448,10 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>3826</v>
+        <v>3821</v>
       </c>
       <c r="B546" t="s">
-        <v>2776</v>
+        <v>2773</v>
       </c>
       <c r="C546" t="s">
         <v>9</v>
@@ -21461,10 +21465,10 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>3827</v>
+        <v>3822</v>
       </c>
       <c r="B547" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="C547" t="s">
         <v>9</v>
@@ -21478,10 +21482,10 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>3828</v>
+        <v>3823</v>
       </c>
       <c r="B548" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="C548" t="s">
         <v>9</v>
@@ -21495,10 +21499,10 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>3829</v>
+        <v>3824</v>
       </c>
       <c r="B549" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C549" t="s">
         <v>9</v>
@@ -21512,10 +21516,10 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>3830</v>
+        <v>3825</v>
       </c>
       <c r="B550" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="C550" t="s">
         <v>9</v>
@@ -21529,10 +21533,10 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>3831</v>
+        <v>3826</v>
       </c>
       <c r="B551" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="C551" t="s">
         <v>9</v>
@@ -21546,10 +21550,10 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>3832</v>
+        <v>3827</v>
       </c>
       <c r="B552" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="C552" t="s">
         <v>9</v>
@@ -21563,10 +21567,10 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>3833</v>
+        <v>3828</v>
       </c>
       <c r="B553" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="C553" t="s">
         <v>9</v>
@@ -21580,10 +21584,10 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>3834</v>
+        <v>3829</v>
       </c>
       <c r="B554" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
       <c r="C554" t="s">
         <v>9</v>
@@ -21597,10 +21601,10 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>3835</v>
+        <v>3830</v>
       </c>
       <c r="B555" t="s">
-        <v>2800</v>
+        <v>2789</v>
       </c>
       <c r="C555" t="s">
         <v>9</v>
@@ -21614,10 +21618,10 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>3836</v>
+        <v>3831</v>
       </c>
       <c r="B556" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="C556" t="s">
         <v>9</v>
@@ -21631,10 +21635,10 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>3837</v>
+        <v>3832</v>
       </c>
       <c r="B557" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="C557" t="s">
         <v>9</v>
@@ -21648,10 +21652,10 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>3838</v>
+        <v>3833</v>
       </c>
       <c r="B558" t="s">
-        <v>2810</v>
+        <v>2799</v>
       </c>
       <c r="C558" t="s">
         <v>9</v>
@@ -21665,10 +21669,10 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>3839</v>
+        <v>3834</v>
       </c>
       <c r="B559" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
       <c r="C559" t="s">
         <v>9</v>
@@ -21682,10 +21686,10 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B560" t="s">
-        <v>2818</v>
+        <v>2813</v>
       </c>
       <c r="C560" t="s">
         <v>9</v>
@@ -21699,10 +21703,10 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>3800</v>
+        <v>3836</v>
       </c>
       <c r="B561" t="s">
-        <v>2246</v>
+        <v>2818</v>
       </c>
       <c r="C561" t="s">
         <v>9</v>
@@ -21716,10 +21720,10 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>3841</v>
+        <v>3796</v>
       </c>
       <c r="B562" t="s">
-        <v>2821</v>
+        <v>2246</v>
       </c>
       <c r="C562" t="s">
         <v>9</v>
@@ -21733,10 +21737,10 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>3842</v>
+        <v>3837</v>
       </c>
       <c r="B563" t="s">
-        <v>2823</v>
+        <v>2821</v>
       </c>
       <c r="C563" t="s">
         <v>9</v>
@@ -21750,10 +21754,10 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>3843</v>
+        <v>3838</v>
       </c>
       <c r="B564" t="s">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="C564" t="s">
         <v>9</v>
@@ -21767,10 +21771,10 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>3844</v>
+        <v>3839</v>
       </c>
       <c r="B565" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="C565" t="s">
         <v>9</v>
@@ -21784,10 +21788,10 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>3845</v>
+        <v>3840</v>
       </c>
       <c r="B566" t="s">
-        <v>2838</v>
+        <v>2828</v>
       </c>
       <c r="C566" t="s">
         <v>9</v>
@@ -21801,10 +21805,10 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>3846</v>
+        <v>3841</v>
       </c>
       <c r="B567" t="s">
-        <v>2835</v>
+        <v>2838</v>
       </c>
       <c r="C567" t="s">
         <v>9</v>
@@ -21818,16 +21822,16 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>3847</v>
+        <v>3842</v>
       </c>
       <c r="B568" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="C568" t="s">
         <v>9</v>
       </c>
       <c r="E568" t="s">
-        <v>993</v>
+        <v>10</v>
       </c>
       <c r="F568" t="s">
         <v>11</v>
@@ -21835,16 +21839,16 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>3848</v>
+        <v>3843</v>
       </c>
       <c r="B569" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="C569" t="s">
         <v>9</v>
       </c>
       <c r="E569" t="s">
-        <v>10</v>
+        <v>993</v>
       </c>
       <c r="F569" t="s">
         <v>11</v>
@@ -21852,10 +21856,10 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>3849</v>
+        <v>3844</v>
       </c>
       <c r="B570" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="C570" t="s">
         <v>9</v>
@@ -21869,10 +21873,10 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>3850</v>
+        <v>3845</v>
       </c>
       <c r="B571" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="C571" t="s">
         <v>9</v>
@@ -21886,10 +21890,10 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>3851</v>
+        <v>3846</v>
       </c>
       <c r="B572" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="C572" t="s">
         <v>9</v>
@@ -21903,10 +21907,10 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>3852</v>
+        <v>3847</v>
       </c>
       <c r="B573" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="C573" t="s">
         <v>9</v>
@@ -21920,10 +21924,10 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>3853</v>
+        <v>3848</v>
       </c>
       <c r="B574" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="C574" t="s">
         <v>9</v>
@@ -21937,10 +21941,10 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>3854</v>
+        <v>3849</v>
       </c>
       <c r="B575" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="C575" t="s">
         <v>9</v>
@@ -21954,10 +21958,10 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>3801</v>
+        <v>3850</v>
       </c>
       <c r="B576" t="s">
-        <v>2274</v>
+        <v>2846</v>
       </c>
       <c r="C576" t="s">
         <v>9</v>
@@ -21971,10 +21975,10 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>3855</v>
+        <v>3797</v>
       </c>
       <c r="B577" t="s">
-        <v>2848</v>
+        <v>2274</v>
       </c>
       <c r="C577" t="s">
         <v>9</v>
@@ -21988,10 +21992,10 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>3856</v>
+        <v>3851</v>
       </c>
       <c r="B578" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="C578" t="s">
         <v>9</v>
@@ -22005,10 +22009,10 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>3857</v>
+        <v>3852</v>
       </c>
       <c r="B579" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
       <c r="C579" t="s">
         <v>9</v>
@@ -22022,10 +22026,10 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>3858</v>
+        <v>3853</v>
       </c>
       <c r="B580" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="C580" t="s">
         <v>9</v>
@@ -22039,10 +22043,10 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>3859</v>
+        <v>3854</v>
       </c>
       <c r="B581" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C581" t="s">
         <v>9</v>
@@ -22056,10 +22060,10 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>3860</v>
+        <v>3855</v>
       </c>
       <c r="B582" t="s">
-        <v>2864</v>
+        <v>2851</v>
       </c>
       <c r="C582" t="s">
         <v>9</v>
@@ -22073,10 +22077,10 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>3861</v>
+        <v>3856</v>
       </c>
       <c r="B583" t="s">
-        <v>2852</v>
+        <v>2864</v>
       </c>
       <c r="C583" t="s">
         <v>9</v>
@@ -22090,10 +22094,10 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>3862</v>
+        <v>3857</v>
       </c>
       <c r="B584" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C584" t="s">
         <v>9</v>
@@ -22107,10 +22111,10 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>3863</v>
+        <v>3858</v>
       </c>
       <c r="B585" t="s">
-        <v>2856</v>
+        <v>2853</v>
       </c>
       <c r="C585" t="s">
         <v>9</v>
@@ -22124,10 +22128,10 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>3864</v>
+        <v>3859</v>
       </c>
       <c r="B586" t="s">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="C586" t="s">
         <v>9</v>
@@ -22141,10 +22145,10 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>3865</v>
+        <v>3860</v>
       </c>
       <c r="B587" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="C587" t="s">
         <v>9</v>
@@ -22158,10 +22162,10 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>3866</v>
+        <v>3861</v>
       </c>
       <c r="B588" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="C588" t="s">
         <v>9</v>
@@ -22175,10 +22179,10 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>3867</v>
+        <v>3862</v>
       </c>
       <c r="B589" t="s">
-        <v>2866</v>
+        <v>2857</v>
       </c>
       <c r="C589" t="s">
         <v>9</v>
@@ -22192,10 +22196,10 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>3868</v>
+        <v>3863</v>
       </c>
       <c r="B590" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="C590" t="s">
         <v>9</v>
@@ -22209,10 +22213,10 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>3869</v>
+        <v>3864</v>
       </c>
       <c r="B591" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="C591" t="s">
         <v>9</v>
@@ -22226,10 +22230,10 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>3870</v>
+        <v>3865</v>
       </c>
       <c r="B592" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="C592" t="s">
         <v>9</v>
@@ -22243,10 +22247,10 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>3871</v>
+        <v>3866</v>
       </c>
       <c r="B593" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="C593" t="s">
         <v>9</v>
@@ -22260,10 +22264,10 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>3872</v>
+        <v>3867</v>
       </c>
       <c r="B594" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="C594" t="s">
         <v>9</v>
@@ -22277,10 +22281,10 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>3873</v>
+        <v>3868</v>
       </c>
       <c r="B595" t="s">
-        <v>2883</v>
+        <v>2876</v>
       </c>
       <c r="C595" t="s">
         <v>9</v>
@@ -22294,10 +22298,10 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>3874</v>
+        <v>3869</v>
       </c>
       <c r="B596" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="C596" t="s">
         <v>9</v>
@@ -22311,10 +22315,10 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>3875</v>
+        <v>3870</v>
       </c>
       <c r="B597" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="C597" t="s">
         <v>9</v>
@@ -22328,10 +22332,10 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>3876</v>
+        <v>3871</v>
       </c>
       <c r="B598" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="C598" t="s">
         <v>9</v>
@@ -22345,10 +22349,10 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>3877</v>
+        <v>3872</v>
       </c>
       <c r="B599" t="s">
-        <v>2888</v>
+        <v>2886</v>
       </c>
       <c r="C599" t="s">
         <v>9</v>
@@ -22362,10 +22366,10 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>3878</v>
+        <v>3873</v>
       </c>
       <c r="B600" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="C600" t="s">
         <v>9</v>
@@ -22379,10 +22383,10 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>3879</v>
+        <v>3874</v>
       </c>
       <c r="B601" t="s">
-        <v>2891</v>
+        <v>2889</v>
       </c>
       <c r="C601" t="s">
         <v>9</v>
@@ -22396,10 +22400,10 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>3880</v>
+        <v>3875</v>
       </c>
       <c r="B602" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="C602" t="s">
         <v>9</v>
@@ -22413,10 +22417,10 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>3881</v>
+        <v>3876</v>
       </c>
       <c r="B603" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="C603" t="s">
         <v>9</v>
@@ -22430,10 +22434,10 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>3882</v>
+        <v>3877</v>
       </c>
       <c r="B604" t="s">
-        <v>2911</v>
+        <v>2894</v>
       </c>
       <c r="C604" t="s">
         <v>9</v>
@@ -22447,7 +22451,7 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>3883</v>
+        <v>3879</v>
       </c>
       <c r="B605" t="s">
         <v>2897</v>
@@ -22464,7 +22468,7 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>3884</v>
+        <v>3880</v>
       </c>
       <c r="B606" t="s">
         <v>2899</v>
@@ -22481,7 +22485,7 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>3885</v>
+        <v>3881</v>
       </c>
       <c r="B607" t="s">
         <v>2900</v>
@@ -22498,7 +22502,7 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>3886</v>
+        <v>3882</v>
       </c>
       <c r="B608" t="s">
         <v>2906</v>
@@ -22515,7 +22519,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>3887</v>
+        <v>3883</v>
       </c>
       <c r="B609" t="s">
         <v>2907</v>
@@ -22532,7 +22536,7 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>3888</v>
+        <v>3884</v>
       </c>
       <c r="B610" t="s">
         <v>2913</v>
@@ -22549,7 +22553,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>3889</v>
+        <v>3885</v>
       </c>
       <c r="B611" t="s">
         <v>2912</v>
@@ -22566,7 +22570,7 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>3890</v>
+        <v>3886</v>
       </c>
       <c r="B612" t="s">
         <v>2914</v>
@@ -22583,7 +22587,7 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>3891</v>
+        <v>3887</v>
       </c>
       <c r="B613" t="s">
         <v>2916</v>
@@ -22600,7 +22604,7 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>3892</v>
+        <v>3888</v>
       </c>
       <c r="B614" t="s">
         <v>2919</v>
@@ -22617,7 +22621,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>3893</v>
+        <v>3889</v>
       </c>
       <c r="B615" t="s">
         <v>2920</v>
@@ -22634,7 +22638,7 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>3894</v>
+        <v>3890</v>
       </c>
       <c r="B616" t="s">
         <v>2918</v>
@@ -22651,7 +22655,7 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>3895</v>
+        <v>3891</v>
       </c>
       <c r="B617" t="s">
         <v>2923</v>
@@ -22668,7 +22672,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>3896</v>
+        <v>3892</v>
       </c>
       <c r="B618" t="s">
         <v>2925</v>
@@ -22685,7 +22689,7 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>3897</v>
+        <v>3893</v>
       </c>
       <c r="B619" t="s">
         <v>2924</v>
@@ -22702,7 +22706,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>3898</v>
+        <v>3894</v>
       </c>
       <c r="B620" t="s">
         <v>2926</v>
@@ -22719,7 +22723,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>3899</v>
+        <v>3895</v>
       </c>
       <c r="B621" t="s">
         <v>2927</v>
@@ -22736,7 +22740,7 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>3900</v>
+        <v>3896</v>
       </c>
       <c r="B622" t="s">
         <v>2928</v>
@@ -22753,7 +22757,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>3901</v>
+        <v>3897</v>
       </c>
       <c r="B623" t="s">
         <v>2929</v>
@@ -22770,7 +22774,7 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>3902</v>
+        <v>3898</v>
       </c>
       <c r="B624" t="s">
         <v>2930</v>
@@ -22787,7 +22791,7 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>3903</v>
+        <v>3899</v>
       </c>
       <c r="B625" t="s">
         <v>2933</v>
@@ -22804,7 +22808,7 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>3904</v>
+        <v>3900</v>
       </c>
       <c r="B626" t="s">
         <v>2932</v>
@@ -22824,10 +22828,10 @@
         <v>3661</v>
       </c>
       <c r="B627" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="C627" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E627" t="s">
         <v>10</v>
@@ -22838,13 +22842,13 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="B628" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="C628" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E628" t="s">
         <v>10</v>
@@ -22855,13 +22859,13 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="B629" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="C629" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E629" t="s">
         <v>10</v>
@@ -22872,13 +22876,13 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="B630" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="C630" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E630" t="s">
         <v>10</v>
@@ -22889,13 +22893,13 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="B631" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="C631" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E631" t="s">
         <v>10</v>
@@ -22906,13 +22910,13 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="B632" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="C632" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E632" t="s">
         <v>10</v>
@@ -22923,13 +22927,13 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="B633" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="C633" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E633" t="s">
         <v>10</v>
@@ -22940,13 +22944,13 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="B634" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="C634" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="E634" t="s">
         <v>10</v>
@@ -22957,14 +22961,14 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="B635" t="s">
+        <v>3792</v>
+      </c>
+      <c r="C635" t="s">
         <v>3793</v>
       </c>
-      <c r="C635" t="s">
-        <v>3794</v>
-      </c>
       <c r="E635" t="s">
         <v>10</v>
       </c>
@@ -22973,11 +22977,11 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A522:B626">
-    <sortCondition ref="A522:A626"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A523:B626">
+    <sortCondition ref="A523:A626"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A490 A494:A1048576">
+  <conditionalFormatting sqref="A494:A1048576 A1:A490">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JSYD.xlsx
+++ b/JSYD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\zb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B5580C-3987-49C3-AA92-6836B38331BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3609C1-7213-4152-AA91-DC550A40338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3477" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3477" uniqueCount="1138">
   <si>
     <t>频道名称</t>
   </si>
@@ -2417,17 +2417,10 @@
     <t>NewTV</t>
   </si>
   <si>
-    <t>江苏</t>
-  </si>
-  <si>
     <t>其他</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>播放异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>咪视界-1</t>
   </si>
   <si>
@@ -3519,6 +3512,10 @@
   </si>
   <si>
     <t>8549</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏地方</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3581,48 +3578,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{72A2AC69-15F3-4E69-8D73-69608530F8C2}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3948,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10793,10 +10749,10 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B344" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C344" t="s">
         <v>789</v>
@@ -10813,10 +10769,10 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B345" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C345" t="s">
         <v>789</v>
@@ -10833,10 +10789,10 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B346" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C346" t="s">
         <v>789</v>
@@ -10853,10 +10809,10 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B347" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C347" t="s">
         <v>789</v>
@@ -10873,10 +10829,10 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B348" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C348" t="s">
         <v>789</v>
@@ -10893,10 +10849,10 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B349" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C349" t="s">
         <v>789</v>
@@ -10913,10 +10869,10 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B350" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C350" t="s">
         <v>789</v>
@@ -10933,10 +10889,10 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B351" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C351" t="s">
         <v>789</v>
@@ -10953,10 +10909,10 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B352" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C352" t="s">
         <v>789</v>
@@ -10973,10 +10929,10 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B353" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C353" t="s">
         <v>789</v>
@@ -10993,10 +10949,10 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B354" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C354" t="s">
         <v>789</v>
@@ -11013,10 +10969,10 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B355" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C355" t="s">
         <v>789</v>
@@ -11033,10 +10989,10 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B356" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C356" t="s">
         <v>789</v>
@@ -11053,10 +11009,10 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B357" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C357" t="s">
         <v>789</v>
@@ -11073,10 +11029,10 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B358" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C358" t="s">
         <v>789</v>
@@ -11093,10 +11049,10 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B359" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C359" t="s">
         <v>789</v>
@@ -11113,10 +11069,10 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B360" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C360" t="s">
         <v>789</v>
@@ -11133,10 +11089,10 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B361" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C361" t="s">
         <v>789</v>
@@ -11153,10 +11109,10 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B362" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C362" t="s">
         <v>789</v>
@@ -11173,10 +11129,10 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B363" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C363" t="s">
         <v>789</v>
@@ -11193,10 +11149,10 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B364" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C364" t="s">
         <v>789</v>
@@ -11213,10 +11169,10 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B365" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C365" t="s">
         <v>789</v>
@@ -11233,10 +11189,10 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B366" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C366" t="s">
         <v>789</v>
@@ -11253,10 +11209,10 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B367" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C367" t="s">
         <v>789</v>
@@ -11273,10 +11229,10 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B368" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C368" t="s">
         <v>789</v>
@@ -11293,10 +11249,10 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B369" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C369" t="s">
         <v>789</v>
@@ -11313,10 +11269,10 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B370" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C370" t="s">
         <v>789</v>
@@ -11333,10 +11289,10 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B371" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C371" t="s">
         <v>789</v>
@@ -11353,10 +11309,10 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B372" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C372" t="s">
         <v>789</v>
@@ -11373,10 +11329,10 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B373" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C373" t="s">
         <v>789</v>
@@ -11393,16 +11349,16 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="B374" t="s">
-        <v>137</v>
+        <v>488</v>
       </c>
       <c r="C374" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E374" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F374" t="s">
         <v>8</v>
@@ -11413,16 +11369,16 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>640</v>
+        <v>783</v>
       </c>
       <c r="B375" t="s">
-        <v>136</v>
+        <v>486</v>
       </c>
       <c r="C375" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E375" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F375" t="s">
         <v>8</v>
@@ -11433,16 +11389,16 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>696</v>
+        <v>778</v>
       </c>
       <c r="B376" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
       <c r="C376" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E376" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F376" t="s">
         <v>8</v>
@@ -11453,16 +11409,16 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>764</v>
+        <v>601</v>
       </c>
       <c r="B377" t="s">
-        <v>113</v>
+        <v>517</v>
       </c>
       <c r="C377" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E377" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F377" t="s">
         <v>8</v>
@@ -11473,16 +11429,16 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>694</v>
+        <v>608</v>
       </c>
       <c r="B378" t="s">
-        <v>142</v>
+        <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E378" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F378" t="s">
         <v>8</v>
@@ -11493,16 +11449,16 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>662</v>
+        <v>613</v>
       </c>
       <c r="B379" t="s">
-        <v>143</v>
+        <v>403</v>
       </c>
       <c r="C379" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E379" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F379" t="s">
         <v>8</v>
@@ -11513,16 +11469,16 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>706</v>
+        <v>604</v>
       </c>
       <c r="B380" t="s">
-        <v>144</v>
+        <v>323</v>
       </c>
       <c r="C380" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E380" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F380" t="s">
         <v>8</v>
@@ -11533,16 +11489,16 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>632</v>
+        <v>604</v>
       </c>
       <c r="B381" t="s">
-        <v>148</v>
+        <v>371</v>
       </c>
       <c r="C381" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E381" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F381" t="s">
         <v>8</v>
@@ -11553,16 +11509,16 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>724</v>
+        <v>610</v>
       </c>
       <c r="B382" t="s">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="C382" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E382" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F382" t="s">
         <v>8</v>
@@ -11573,16 +11529,16 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>655</v>
+        <v>610</v>
       </c>
       <c r="B383" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
       <c r="C383" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E383" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F383" t="s">
         <v>8</v>
@@ -11593,16 +11549,16 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>705</v>
+        <v>617</v>
       </c>
       <c r="B384" t="s">
-        <v>176</v>
+        <v>326</v>
       </c>
       <c r="C384" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E384" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F384" t="s">
         <v>8</v>
@@ -11613,16 +11569,16 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>683</v>
+        <v>784</v>
       </c>
       <c r="B385" t="s">
-        <v>175</v>
+        <v>573</v>
       </c>
       <c r="C385" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E385" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F385" t="s">
         <v>8</v>
@@ -11633,16 +11589,16 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>713</v>
+        <v>785</v>
       </c>
       <c r="B386" t="s">
-        <v>173</v>
+        <v>560</v>
       </c>
       <c r="C386" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E386" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F386" t="s">
         <v>8</v>
@@ -11653,16 +11609,16 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>704</v>
+        <v>787</v>
       </c>
       <c r="B387" t="s">
-        <v>181</v>
+        <v>558</v>
       </c>
       <c r="C387" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E387" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F387" t="s">
         <v>8</v>
@@ -11673,16 +11629,16 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>701</v>
+        <v>786</v>
       </c>
       <c r="B388" t="s">
-        <v>183</v>
+        <v>554</v>
       </c>
       <c r="C388" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E388" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F388" t="s">
         <v>8</v>
@@ -11693,16 +11649,16 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>702</v>
+        <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>147</v>
+        <v>578</v>
       </c>
       <c r="C389" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E389" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F389" t="s">
         <v>8</v>
@@ -11713,16 +11669,16 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>703</v>
+        <v>592</v>
       </c>
       <c r="B390" t="s">
-        <v>385</v>
+        <v>129</v>
       </c>
       <c r="C390" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E390" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F390" t="s">
         <v>8</v>
@@ -11733,16 +11689,16 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>768</v>
+        <v>593</v>
       </c>
       <c r="B391" t="s">
-        <v>179</v>
+        <v>356</v>
       </c>
       <c r="C391" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E391" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F391" t="s">
         <v>8</v>
@@ -11753,16 +11709,16 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>667</v>
+        <v>594</v>
       </c>
       <c r="B392" t="s">
-        <v>141</v>
+        <v>310</v>
       </c>
       <c r="C392" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E392" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F392" t="s">
         <v>8</v>
@@ -11773,16 +11729,16 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>731</v>
+        <v>878</v>
       </c>
       <c r="B393" t="s">
-        <v>130</v>
+        <v>880</v>
       </c>
       <c r="C393" t="s">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="E393" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F393" t="s">
         <v>8</v>
@@ -11793,16 +11749,16 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>721</v>
+        <v>879</v>
       </c>
       <c r="B394" t="s">
-        <v>396</v>
+        <v>881</v>
       </c>
       <c r="C394" t="s">
-        <v>791</v>
+        <v>590</v>
       </c>
       <c r="E394" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F394" t="s">
         <v>8</v>
@@ -11813,16 +11769,16 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>720</v>
+        <v>1008</v>
       </c>
       <c r="B395" t="s">
-        <v>391</v>
+        <v>882</v>
       </c>
       <c r="C395" t="s">
-        <v>791</v>
+        <v>590</v>
       </c>
       <c r="E395" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F395" t="s">
         <v>8</v>
@@ -11832,17 +11788,17 @@
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
-        <v>641</v>
+      <c r="A396" s="1" t="s">
+        <v>1009</v>
       </c>
       <c r="B396" t="s">
-        <v>392</v>
+        <v>524</v>
       </c>
       <c r="C396" t="s">
-        <v>791</v>
+        <v>590</v>
       </c>
       <c r="E396" t="s">
-        <v>7</v>
+        <v>779</v>
       </c>
       <c r="F396" t="s">
         <v>8</v>
@@ -11852,17 +11808,17 @@
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
-        <v>854</v>
+      <c r="A397" s="1" t="s">
+        <v>1010</v>
       </c>
       <c r="B397" t="s">
-        <v>855</v>
+        <v>423</v>
       </c>
       <c r="C397" t="s">
-        <v>791</v>
+        <v>590</v>
       </c>
       <c r="E397" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F397" t="s">
         <v>8</v>
@@ -11872,17 +11828,17 @@
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>691</v>
+      <c r="A398" s="1" t="s">
+        <v>1011</v>
       </c>
       <c r="B398" t="s">
-        <v>514</v>
+        <v>577</v>
       </c>
       <c r="C398" t="s">
-        <v>791</v>
+        <v>590</v>
       </c>
       <c r="E398" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F398" t="s">
         <v>8</v>
@@ -11893,13 +11849,13 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>692</v>
+        <v>774</v>
       </c>
       <c r="B399" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C399" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E399" t="s">
         <v>7</v>
@@ -11913,13 +11869,13 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>692</v>
+        <v>640</v>
       </c>
       <c r="B400" t="s">
-        <v>516</v>
+        <v>136</v>
       </c>
       <c r="C400" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E400" t="s">
         <v>7</v>
@@ -11933,13 +11889,13 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="B401" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="C401" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E401" t="s">
         <v>7</v>
@@ -11953,13 +11909,13 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="B402" t="s">
-        <v>518</v>
+        <v>113</v>
       </c>
       <c r="C402" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E402" t="s">
         <v>7</v>
@@ -11973,13 +11929,13 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B403" t="s">
-        <v>525</v>
+        <v>142</v>
       </c>
       <c r="C403" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E403" t="s">
         <v>7</v>
@@ -11993,13 +11949,13 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="B404" t="s">
-        <v>435</v>
+        <v>143</v>
       </c>
       <c r="C404" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E404" t="s">
         <v>7</v>
@@ -12013,13 +11969,13 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="B405" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="C405" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E405" t="s">
         <v>7</v>
@@ -12033,13 +11989,13 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>688</v>
+        <v>632</v>
       </c>
       <c r="B406" t="s">
-        <v>527</v>
+        <v>148</v>
       </c>
       <c r="C406" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E406" t="s">
         <v>7</v>
@@ -12053,13 +12009,13 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="B407" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C407" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E407" t="s">
         <v>7</v>
@@ -12073,13 +12029,13 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>717</v>
+        <v>655</v>
       </c>
       <c r="B408" t="s">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="C408" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E408" t="s">
         <v>7</v>
@@ -12093,13 +12049,13 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="B409" t="s">
-        <v>246</v>
+        <v>176</v>
       </c>
       <c r="C409" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E409" t="s">
         <v>7</v>
@@ -12113,13 +12069,13 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>716</v>
+        <v>683</v>
       </c>
       <c r="B410" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="C410" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E410" t="s">
         <v>7</v>
@@ -12133,13 +12089,13 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B411" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="C411" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E411" t="s">
         <v>7</v>
@@ -12153,13 +12109,13 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B412" t="s">
-        <v>254</v>
+        <v>181</v>
       </c>
       <c r="C412" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E412" t="s">
         <v>7</v>
@@ -12173,13 +12129,13 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B413" t="s">
-        <v>551</v>
+        <v>183</v>
       </c>
       <c r="C413" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E413" t="s">
         <v>7</v>
@@ -12193,13 +12149,13 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>856</v>
+        <v>702</v>
       </c>
       <c r="B414" t="s">
-        <v>861</v>
+        <v>147</v>
       </c>
       <c r="C414" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E414" t="s">
         <v>7</v>
@@ -12213,13 +12169,13 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>857</v>
+        <v>703</v>
       </c>
       <c r="B415" t="s">
-        <v>862</v>
+        <v>385</v>
       </c>
       <c r="C415" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E415" t="s">
         <v>7</v>
@@ -12233,13 +12189,13 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>858</v>
+        <v>768</v>
       </c>
       <c r="B416" t="s">
-        <v>863</v>
+        <v>179</v>
       </c>
       <c r="C416" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E416" t="s">
         <v>7</v>
@@ -12253,13 +12209,13 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>859</v>
+        <v>667</v>
       </c>
       <c r="B417" t="s">
-        <v>864</v>
+        <v>141</v>
       </c>
       <c r="C417" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E417" t="s">
         <v>7</v>
@@ -12273,13 +12229,13 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>860</v>
+        <v>731</v>
       </c>
       <c r="B418" t="s">
-        <v>865</v>
+        <v>130</v>
       </c>
       <c r="C418" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E418" t="s">
         <v>7</v>
@@ -12293,13 +12249,13 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>754</v>
+        <v>721</v>
       </c>
       <c r="B419" t="s">
-        <v>291</v>
+        <v>396</v>
       </c>
       <c r="C419" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E419" t="s">
         <v>7</v>
@@ -12313,13 +12269,13 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>903</v>
+        <v>720</v>
       </c>
       <c r="B420" t="s">
-        <v>571</v>
+        <v>391</v>
       </c>
       <c r="C420" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E420" t="s">
         <v>7</v>
@@ -12333,13 +12289,13 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>904</v>
+        <v>641</v>
       </c>
       <c r="B421" t="s">
-        <v>587</v>
+        <v>392</v>
       </c>
       <c r="C421" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E421" t="s">
         <v>7</v>
@@ -12353,13 +12309,13 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>639</v>
+        <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>262</v>
+        <v>853</v>
       </c>
       <c r="C422" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E422" t="s">
         <v>7</v>
@@ -12373,13 +12329,13 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>639</v>
+        <v>691</v>
       </c>
       <c r="B423" t="s">
-        <v>272</v>
+        <v>514</v>
       </c>
       <c r="C423" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E423" t="s">
         <v>7</v>
@@ -12393,13 +12349,13 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="B424" t="s">
-        <v>264</v>
+        <v>39</v>
       </c>
       <c r="C424" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E424" t="s">
         <v>7</v>
@@ -12413,13 +12369,13 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="B425" t="s">
-        <v>275</v>
+        <v>516</v>
       </c>
       <c r="C425" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E425" t="s">
         <v>7</v>
@@ -12433,13 +12389,13 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>638</v>
+        <v>686</v>
       </c>
       <c r="B426" t="s">
-        <v>270</v>
+        <v>38</v>
       </c>
       <c r="C426" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E426" t="s">
         <v>7</v>
@@ -12453,13 +12409,13 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>638</v>
+        <v>686</v>
       </c>
       <c r="B427" t="s">
-        <v>273</v>
+        <v>518</v>
       </c>
       <c r="C427" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E427" t="s">
         <v>7</v>
@@ -12473,13 +12429,13 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B428" t="s">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="C428" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E428" t="s">
         <v>7</v>
@@ -12493,13 +12449,13 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>765</v>
+        <v>687</v>
       </c>
       <c r="B429" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="C429" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E429" t="s">
         <v>7</v>
@@ -12513,13 +12469,13 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>766</v>
+        <v>688</v>
       </c>
       <c r="B430" t="s">
-        <v>386</v>
+        <v>40</v>
       </c>
       <c r="C430" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E430" t="s">
         <v>7</v>
@@ -12533,13 +12489,13 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>767</v>
+        <v>688</v>
       </c>
       <c r="B431" t="s">
-        <v>389</v>
+        <v>527</v>
       </c>
       <c r="C431" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E431" t="s">
         <v>7</v>
@@ -12553,13 +12509,13 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>866</v>
+        <v>718</v>
       </c>
       <c r="B432" t="s">
-        <v>868</v>
+        <v>63</v>
       </c>
       <c r="C432" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E432" t="s">
         <v>7</v>
@@ -12573,13 +12529,13 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>867</v>
+        <v>717</v>
       </c>
       <c r="B433" t="s">
-        <v>869</v>
+        <v>248</v>
       </c>
       <c r="C433" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E433" t="s">
         <v>7</v>
@@ -12593,13 +12549,13 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>760</v>
+        <v>719</v>
       </c>
       <c r="B434" t="s">
-        <v>41</v>
+        <v>246</v>
       </c>
       <c r="C434" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E434" t="s">
         <v>7</v>
@@ -12613,13 +12569,13 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>761</v>
+        <v>716</v>
       </c>
       <c r="B435" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C435" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E435" t="s">
         <v>7</v>
@@ -12633,13 +12589,13 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>762</v>
+        <v>714</v>
       </c>
       <c r="B436" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C436" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E436" t="s">
         <v>7</v>
@@ -12653,13 +12609,13 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>763</v>
+        <v>715</v>
       </c>
       <c r="B437" t="s">
-        <v>44</v>
+        <v>254</v>
       </c>
       <c r="C437" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E437" t="s">
         <v>7</v>
@@ -12673,13 +12629,13 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>758</v>
+        <v>707</v>
       </c>
       <c r="B438" t="s">
-        <v>72</v>
+        <v>551</v>
       </c>
       <c r="C438" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E438" t="s">
         <v>7</v>
@@ -12693,13 +12649,13 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>750</v>
+        <v>854</v>
       </c>
       <c r="B439" t="s">
-        <v>316</v>
+        <v>859</v>
       </c>
       <c r="C439" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E439" t="s">
         <v>7</v>
@@ -12713,13 +12669,13 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>751</v>
+        <v>855</v>
       </c>
       <c r="B440" t="s">
-        <v>282</v>
+        <v>860</v>
       </c>
       <c r="C440" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E440" t="s">
         <v>7</v>
@@ -12733,13 +12689,13 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>752</v>
+        <v>856</v>
       </c>
       <c r="B441" t="s">
-        <v>280</v>
+        <v>861</v>
       </c>
       <c r="C441" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E441" t="s">
         <v>7</v>
@@ -12753,13 +12709,13 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>753</v>
+        <v>857</v>
       </c>
       <c r="B442" t="s">
-        <v>357</v>
+        <v>862</v>
       </c>
       <c r="C442" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E442" t="s">
         <v>7</v>
@@ -12773,13 +12729,13 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>727</v>
+        <v>858</v>
       </c>
       <c r="B443" t="s">
-        <v>217</v>
+        <v>863</v>
       </c>
       <c r="C443" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E443" t="s">
         <v>7</v>
@@ -12793,13 +12749,13 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>725</v>
+        <v>754</v>
       </c>
       <c r="B444" t="s">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="C444" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E444" t="s">
         <v>7</v>
@@ -12813,13 +12769,13 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>726</v>
+        <v>901</v>
       </c>
       <c r="B445" t="s">
-        <v>221</v>
+        <v>571</v>
       </c>
       <c r="C445" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E445" t="s">
         <v>7</v>
@@ -12833,13 +12789,13 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>744</v>
+        <v>902</v>
       </c>
       <c r="B446" t="s">
-        <v>240</v>
+        <v>587</v>
       </c>
       <c r="C446" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E446" t="s">
         <v>7</v>
@@ -12853,13 +12809,13 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>744</v>
+        <v>639</v>
       </c>
       <c r="B447" t="s">
-        <v>870</v>
+        <v>262</v>
       </c>
       <c r="C447" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E447" t="s">
         <v>7</v>
@@ -12873,13 +12829,13 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>742</v>
+        <v>639</v>
       </c>
       <c r="B448" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C448" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E448" t="s">
         <v>7</v>
@@ -12893,13 +12849,13 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>743</v>
+        <v>637</v>
       </c>
       <c r="B449" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C449" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E449" t="s">
         <v>7</v>
@@ -12913,13 +12869,13 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>771</v>
+        <v>637</v>
       </c>
       <c r="B450" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="C450" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E450" t="s">
         <v>7</v>
@@ -12933,13 +12889,13 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>772</v>
+        <v>638</v>
       </c>
       <c r="B451" t="s">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="C451" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E451" t="s">
         <v>7</v>
@@ -12953,13 +12909,13 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>773</v>
+        <v>638</v>
       </c>
       <c r="B452" t="s">
-        <v>338</v>
+        <v>273</v>
       </c>
       <c r="C452" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E452" t="s">
         <v>7</v>
@@ -12973,13 +12929,13 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>634</v>
+        <v>695</v>
       </c>
       <c r="B453" t="s">
-        <v>276</v>
+        <v>564</v>
       </c>
       <c r="C453" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E453" t="s">
         <v>7</v>
@@ -12993,13 +12949,13 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>685</v>
+        <v>765</v>
       </c>
       <c r="B454" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C454" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E454" t="s">
         <v>7</v>
@@ -13013,13 +12969,13 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="B455" t="s">
-        <v>339</v>
+        <v>386</v>
       </c>
       <c r="C455" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E455" t="s">
         <v>7</v>
@@ -13033,13 +12989,13 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="B456" t="s">
-        <v>340</v>
+        <v>389</v>
       </c>
       <c r="C456" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E456" t="s">
         <v>7</v>
@@ -13053,13 +13009,13 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>747</v>
+        <v>864</v>
       </c>
       <c r="B457" t="s">
-        <v>289</v>
+        <v>866</v>
       </c>
       <c r="C457" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E457" t="s">
         <v>7</v>
@@ -13073,13 +13029,13 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>646</v>
+        <v>865</v>
       </c>
       <c r="B458" t="s">
-        <v>269</v>
+        <v>867</v>
       </c>
       <c r="C458" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E458" t="s">
         <v>7</v>
@@ -13093,13 +13049,13 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>645</v>
+        <v>760</v>
       </c>
       <c r="B459" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="C459" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E459" t="s">
         <v>7</v>
@@ -13113,13 +13069,13 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>661</v>
+        <v>761</v>
       </c>
       <c r="B460" t="s">
-        <v>370</v>
+        <v>42</v>
       </c>
       <c r="C460" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E460" t="s">
         <v>7</v>
@@ -13133,13 +13089,13 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>677</v>
+        <v>762</v>
       </c>
       <c r="B461" t="s">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="C461" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E461" t="s">
         <v>7</v>
@@ -13153,13 +13109,13 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="B462" t="s">
-        <v>557</v>
+        <v>44</v>
       </c>
       <c r="C462" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E462" t="s">
         <v>7</v>
@@ -13173,13 +13129,13 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>676</v>
+        <v>758</v>
       </c>
       <c r="B463" t="s">
-        <v>559</v>
+        <v>72</v>
       </c>
       <c r="C463" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E463" t="s">
         <v>7</v>
@@ -13193,13 +13149,13 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>675</v>
+        <v>750</v>
       </c>
       <c r="B464" t="s">
-        <v>561</v>
+        <v>316</v>
       </c>
       <c r="C464" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E464" t="s">
         <v>7</v>
@@ -13213,13 +13169,13 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B465" t="s">
-        <v>566</v>
+        <v>282</v>
       </c>
       <c r="C465" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E465" t="s">
         <v>7</v>
@@ -13233,13 +13189,13 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>871</v>
+        <v>752</v>
       </c>
       <c r="B466" t="s">
-        <v>873</v>
+        <v>280</v>
       </c>
       <c r="C466" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E466" t="s">
         <v>7</v>
@@ -13253,13 +13209,13 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>872</v>
+        <v>753</v>
       </c>
       <c r="B467" t="s">
-        <v>874</v>
+        <v>357</v>
       </c>
       <c r="C467" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E467" t="s">
         <v>7</v>
@@ -13273,13 +13229,13 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="B468" t="s">
-        <v>47</v>
+        <v>217</v>
       </c>
       <c r="C468" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E468" t="s">
         <v>7</v>
@@ -13293,13 +13249,13 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="B469" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="C469" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E469" t="s">
         <v>7</v>
@@ -13313,13 +13269,13 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="B470" t="s">
-        <v>549</v>
+        <v>221</v>
       </c>
       <c r="C470" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E470" t="s">
         <v>7</v>
@@ -13333,13 +13289,13 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B471" t="s">
-        <v>877</v>
+        <v>240</v>
       </c>
       <c r="C471" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E471" t="s">
         <v>7</v>
@@ -13353,13 +13309,13 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>875</v>
+        <v>744</v>
       </c>
       <c r="B472" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="C472" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E472" t="s">
         <v>7</v>
@@ -13373,13 +13329,13 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>876</v>
+        <v>742</v>
       </c>
       <c r="B473" t="s">
-        <v>879</v>
+        <v>242</v>
       </c>
       <c r="C473" t="s">
-        <v>791</v>
+        <v>1137</v>
       </c>
       <c r="E473" t="s">
         <v>7</v>
@@ -13393,16 +13349,16 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>782</v>
+        <v>743</v>
       </c>
       <c r="B474" t="s">
-        <v>488</v>
+        <v>243</v>
       </c>
       <c r="C474" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E474" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F474" t="s">
         <v>8</v>
@@ -13413,16 +13369,16 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>783</v>
+        <v>728</v>
       </c>
       <c r="B475" t="s">
-        <v>486</v>
+        <v>166</v>
       </c>
       <c r="C475" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E475" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F475" t="s">
         <v>8</v>
@@ -13433,16 +13389,16 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B476" t="s">
-        <v>420</v>
+        <v>355</v>
       </c>
       <c r="C476" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E476" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F476" t="s">
         <v>8</v>
@@ -13453,16 +13409,16 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>601</v>
+        <v>772</v>
       </c>
       <c r="B477" t="s">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="C477" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E477" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F477" t="s">
         <v>8</v>
@@ -13473,16 +13429,16 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>608</v>
+        <v>773</v>
       </c>
       <c r="B478" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="C478" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E478" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F478" t="s">
         <v>8</v>
@@ -13493,16 +13449,16 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="B479" t="s">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="C479" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E479" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F479" t="s">
         <v>8</v>
@@ -13513,16 +13469,16 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>604</v>
+        <v>685</v>
       </c>
       <c r="B480" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="C480" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E480" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F480" t="s">
         <v>8</v>
@@ -13533,16 +13489,16 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>604</v>
+        <v>745</v>
       </c>
       <c r="B481" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="C481" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E481" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F481" t="s">
         <v>8</v>
@@ -13553,16 +13509,16 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>610</v>
+        <v>746</v>
       </c>
       <c r="B482" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C482" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E482" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F482" t="s">
         <v>8</v>
@@ -13573,16 +13529,16 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>610</v>
+        <v>747</v>
       </c>
       <c r="B483" t="s">
-        <v>400</v>
+        <v>289</v>
       </c>
       <c r="C483" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E483" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F483" t="s">
         <v>8</v>
@@ -13593,16 +13549,16 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>617</v>
+        <v>709</v>
       </c>
       <c r="B484" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="C484" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E484" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F484" t="s">
         <v>8</v>
@@ -13613,16 +13569,16 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>784</v>
+        <v>708</v>
       </c>
       <c r="B485" t="s">
-        <v>573</v>
+        <v>271</v>
       </c>
       <c r="C485" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E485" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F485" t="s">
         <v>8</v>
@@ -13633,16 +13589,16 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>785</v>
+        <v>646</v>
       </c>
       <c r="B486" t="s">
-        <v>560</v>
+        <v>269</v>
       </c>
       <c r="C486" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E486" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F486" t="s">
         <v>8</v>
@@ -13653,16 +13609,16 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>787</v>
+        <v>645</v>
       </c>
       <c r="B487" t="s">
-        <v>558</v>
+        <v>257</v>
       </c>
       <c r="C487" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E487" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F487" t="s">
         <v>8</v>
@@ -13673,16 +13629,16 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>592</v>
+        <v>661</v>
       </c>
       <c r="B488" t="s">
-        <v>129</v>
+        <v>370</v>
       </c>
       <c r="C488" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E488" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F488" t="s">
         <v>8</v>
@@ -13693,16 +13649,16 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>593</v>
+        <v>677</v>
       </c>
       <c r="B489" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C489" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E489" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F489" t="s">
         <v>8</v>
@@ -13713,16 +13669,16 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>594</v>
+        <v>677</v>
       </c>
       <c r="B490" t="s">
-        <v>310</v>
+        <v>557</v>
       </c>
       <c r="C490" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E490" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F490" t="s">
         <v>8</v>
@@ -13733,16 +13689,16 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>880</v>
+        <v>676</v>
       </c>
       <c r="B491" t="s">
-        <v>882</v>
+        <v>559</v>
       </c>
       <c r="C491" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E491" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F491" t="s">
         <v>8</v>
@@ -13753,16 +13709,16 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>881</v>
+        <v>675</v>
       </c>
       <c r="B492" t="s">
-        <v>883</v>
+        <v>561</v>
       </c>
       <c r="C492" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E492" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F492" t="s">
         <v>8</v>
@@ -13773,16 +13729,16 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1010</v>
+        <v>759</v>
       </c>
       <c r="B493" t="s">
-        <v>884</v>
+        <v>566</v>
       </c>
       <c r="C493" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E493" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F493" t="s">
         <v>8</v>
@@ -13792,17 +13748,17 @@
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A494" s="1" t="s">
-        <v>1011</v>
+      <c r="A494" t="s">
+        <v>869</v>
       </c>
       <c r="B494" t="s">
-        <v>524</v>
+        <v>871</v>
       </c>
       <c r="C494" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E494" t="s">
-        <v>779</v>
+        <v>7</v>
       </c>
       <c r="F494" t="s">
         <v>8</v>
@@ -13812,17 +13768,17 @@
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A495" s="1" t="s">
-        <v>1012</v>
+      <c r="A495" t="s">
+        <v>870</v>
       </c>
       <c r="B495" t="s">
-        <v>423</v>
+        <v>872</v>
       </c>
       <c r="C495" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E495" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F495" t="s">
         <v>8</v>
@@ -13832,17 +13788,17 @@
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A496" s="1" t="s">
-        <v>1013</v>
+      <c r="A496" t="s">
+        <v>740</v>
       </c>
       <c r="B496" t="s">
-        <v>577</v>
+        <v>47</v>
       </c>
       <c r="C496" t="s">
-        <v>590</v>
+        <v>1137</v>
       </c>
       <c r="E496" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F496" t="s">
         <v>8</v>
@@ -13853,16 +13809,16 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>786</v>
+        <v>741</v>
       </c>
       <c r="B497" t="s">
-        <v>554</v>
+        <v>48</v>
       </c>
       <c r="C497" t="s">
-        <v>793</v>
+        <v>1137</v>
       </c>
       <c r="E497" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F497" t="s">
         <v>8</v>
@@ -13873,16 +13829,16 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>786</v>
+        <v>738</v>
       </c>
       <c r="B498" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="C498" t="s">
-        <v>793</v>
+        <v>1137</v>
       </c>
       <c r="E498" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F498" t="s">
         <v>8</v>
@@ -13893,13 +13849,13 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>709</v>
+        <v>738</v>
       </c>
       <c r="B499" t="s">
-        <v>267</v>
+        <v>875</v>
       </c>
       <c r="C499" t="s">
-        <v>793</v>
+        <v>1137</v>
       </c>
       <c r="E499" t="s">
         <v>7</v>
@@ -13913,13 +13869,13 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>708</v>
+        <v>873</v>
       </c>
       <c r="B500" t="s">
-        <v>271</v>
+        <v>876</v>
       </c>
       <c r="C500" t="s">
-        <v>793</v>
+        <v>1137</v>
       </c>
       <c r="E500" t="s">
         <v>7</v>
@@ -13933,13 +13889,13 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>728</v>
+        <v>874</v>
       </c>
       <c r="B501" t="s">
-        <v>166</v>
+        <v>877</v>
       </c>
       <c r="C501" t="s">
-        <v>793</v>
+        <v>1137</v>
       </c>
       <c r="E501" t="s">
         <v>7</v>
@@ -13953,13 +13909,13 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>987</v>
+        <v>749</v>
       </c>
       <c r="B502" t="s">
-        <v>567</v>
+        <v>404</v>
       </c>
       <c r="C502" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E502" t="s">
         <v>7</v>
@@ -13973,13 +13929,13 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>749</v>
+        <v>642</v>
       </c>
       <c r="B503" t="s">
-        <v>404</v>
+        <v>19</v>
       </c>
       <c r="C503" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E503" t="s">
         <v>7</v>
@@ -13993,13 +13949,13 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="B504" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C504" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E504" t="s">
         <v>7</v>
@@ -14013,13 +13969,13 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B505" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C505" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E505" t="s">
         <v>7</v>
@@ -14036,10 +13992,10 @@
         <v>671</v>
       </c>
       <c r="B506" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="C506" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E506" t="s">
         <v>7</v>
@@ -14053,16 +14009,16 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="B507" t="s">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="C507" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E507" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F507" t="s">
         <v>8</v>
@@ -14073,16 +14029,16 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="B508" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="C508" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E508" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F508" t="s">
         <v>8</v>
@@ -14093,13 +14049,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B509" t="s">
-        <v>459</v>
+        <v>397</v>
       </c>
       <c r="C509" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E509" t="s">
         <v>7</v>
@@ -14113,13 +14069,13 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B510" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C510" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E510" t="s">
         <v>7</v>
@@ -14133,13 +14089,13 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B511" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C511" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E511" t="s">
         <v>7</v>
@@ -14153,13 +14109,13 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B512" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C512" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E512" t="s">
         <v>7</v>
@@ -14173,13 +14129,13 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B513" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="C513" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E513" t="s">
         <v>7</v>
@@ -14193,13 +14149,13 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B514" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C514" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E514" t="s">
         <v>7</v>
@@ -14213,13 +14169,13 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B515" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C515" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E515" t="s">
         <v>7</v>
@@ -14233,13 +14189,13 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="B516" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="C516" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E516" t="s">
         <v>7</v>
@@ -14253,13 +14209,13 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B517" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C517" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E517" t="s">
         <v>7</v>
@@ -14273,13 +14229,13 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B518" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C518" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E518" t="s">
         <v>7</v>
@@ -14293,13 +14249,13 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B519" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="C519" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E519" t="s">
         <v>7</v>
@@ -14313,13 +14269,13 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>684</v>
+        <v>729</v>
       </c>
       <c r="B520" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C520" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E520" t="s">
         <v>7</v>
@@ -14333,13 +14289,13 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="B521" t="s">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="C521" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E521" t="s">
         <v>7</v>
@@ -14353,13 +14309,13 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>756</v>
+        <v>1085</v>
       </c>
       <c r="B522" t="s">
-        <v>481</v>
+        <v>1086</v>
       </c>
       <c r="C522" t="s">
-        <v>792</v>
+        <v>6</v>
       </c>
       <c r="E522" t="s">
         <v>7</v>
@@ -14373,10 +14329,10 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1087</v>
+        <v>905</v>
       </c>
       <c r="B523" t="s">
-        <v>1088</v>
+        <v>30</v>
       </c>
       <c r="C523" t="s">
         <v>6</v>
@@ -14393,10 +14349,10 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B524" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C524" t="s">
         <v>6</v>
@@ -14413,10 +14369,10 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B525" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C525" t="s">
         <v>6</v>
@@ -14433,10 +14389,10 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B526" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C526" t="s">
         <v>6</v>
@@ -14453,10 +14409,10 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B527" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C527" t="s">
         <v>6</v>
@@ -14473,10 +14429,10 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B528" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="C528" t="s">
         <v>6</v>
@@ -14493,10 +14449,10 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B529" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C529" t="s">
         <v>6</v>
@@ -14513,10 +14469,10 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B530" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="C530" t="s">
         <v>6</v>
@@ -14533,16 +14489,16 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B531" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C531" t="s">
         <v>6</v>
       </c>
       <c r="E531" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F531" t="s">
         <v>8</v>
@@ -14553,16 +14509,16 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B532" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C532" t="s">
         <v>6</v>
       </c>
       <c r="E532" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F532" t="s">
         <v>8</v>
@@ -14573,10 +14529,10 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B533" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C533" t="s">
         <v>6</v>
@@ -14593,10 +14549,10 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B534" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C534" t="s">
         <v>6</v>
@@ -14613,10 +14569,10 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B535" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C535" t="s">
         <v>6</v>
@@ -14633,10 +14589,10 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B536" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C536" t="s">
         <v>6</v>
@@ -14653,10 +14609,10 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B537" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C537" t="s">
         <v>6</v>
@@ -14673,10 +14629,10 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B538" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="C538" t="s">
         <v>6</v>
@@ -14693,10 +14649,10 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B539" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C539" t="s">
         <v>6</v>
@@ -14713,10 +14669,10 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B540" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="C540" t="s">
         <v>6</v>
@@ -14733,10 +14689,10 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B541" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C541" t="s">
         <v>6</v>
@@ -14753,10 +14709,10 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B542" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C542" t="s">
         <v>6</v>
@@ -14773,10 +14729,10 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B543" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C543" t="s">
         <v>6</v>
@@ -14793,10 +14749,10 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B544" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C544" t="s">
         <v>6</v>
@@ -14813,10 +14769,10 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B545" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C545" t="s">
         <v>6</v>
@@ -14833,10 +14789,10 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B546" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C546" t="s">
         <v>6</v>
@@ -14853,10 +14809,10 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B547" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C547" t="s">
         <v>6</v>
@@ -14873,10 +14829,10 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B548" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C548" t="s">
         <v>6</v>
@@ -14893,10 +14849,10 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B549" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C549" t="s">
         <v>6</v>
@@ -14913,10 +14869,10 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B550" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C550" t="s">
         <v>6</v>
@@ -14933,10 +14889,10 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B551" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C551" t="s">
         <v>6</v>
@@ -14953,10 +14909,10 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B552" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C552" t="s">
         <v>6</v>
@@ -14973,10 +14929,10 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B553" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C553" t="s">
         <v>6</v>
@@ -14993,10 +14949,10 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B554" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C554" t="s">
         <v>6</v>
@@ -15013,10 +14969,10 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B555" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C555" t="s">
         <v>6</v>
@@ -15033,10 +14989,10 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B556" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C556" t="s">
         <v>6</v>
@@ -15052,14 +15008,14 @@
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A557" t="s">
-        <v>940</v>
+      <c r="A557" s="1" t="s">
+        <v>1088</v>
       </c>
       <c r="B557" t="s">
-        <v>456</v>
+        <v>1082</v>
       </c>
       <c r="C557" t="s">
-        <v>6</v>
+        <v>1087</v>
       </c>
       <c r="E557" t="s">
         <v>7</v>
@@ -15072,14 +15028,14 @@
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A558" s="1" t="s">
-        <v>1090</v>
+      <c r="A558" t="s">
+        <v>939</v>
       </c>
       <c r="B558" t="s">
-        <v>1084</v>
+        <v>453</v>
       </c>
       <c r="C558" t="s">
-        <v>1089</v>
+        <v>6</v>
       </c>
       <c r="E558" t="s">
         <v>7</v>
@@ -15093,10 +15049,10 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B559" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C559" t="s">
         <v>6</v>
@@ -15113,10 +15069,10 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B560" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="C560" t="s">
         <v>6</v>
@@ -15133,10 +15089,10 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B561" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C561" t="s">
         <v>6</v>
@@ -15153,10 +15109,10 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B562" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C562" t="s">
         <v>6</v>
@@ -15173,10 +15129,10 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>945</v>
+        <v>903</v>
       </c>
       <c r="B563" t="s">
-        <v>474</v>
+        <v>13</v>
       </c>
       <c r="C563" t="s">
         <v>6</v>
@@ -15193,10 +15149,10 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>905</v>
+        <v>944</v>
       </c>
       <c r="B564" t="s">
-        <v>13</v>
+        <v>477</v>
       </c>
       <c r="C564" t="s">
         <v>6</v>
@@ -15213,10 +15169,10 @@
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B565" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C565" t="s">
         <v>6</v>
@@ -15233,10 +15189,10 @@
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B566" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C566" t="s">
         <v>6</v>
@@ -15253,10 +15209,10 @@
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B567" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C567" t="s">
         <v>6</v>
@@ -15273,10 +15229,10 @@
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B568" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="C568" t="s">
         <v>6</v>
@@ -15293,10 +15249,10 @@
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B569" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C569" t="s">
         <v>6</v>
@@ -15313,16 +15269,16 @@
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B570" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C570" t="s">
         <v>6</v>
       </c>
       <c r="E570" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F570" t="s">
         <v>8</v>
@@ -15333,16 +15289,16 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B571" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C571" t="s">
         <v>6</v>
       </c>
       <c r="E571" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F571" t="s">
         <v>8</v>
@@ -15353,10 +15309,10 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B572" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C572" t="s">
         <v>6</v>
@@ -15373,10 +15329,10 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B573" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C573" t="s">
         <v>6</v>
@@ -15393,10 +15349,10 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B574" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C574" t="s">
         <v>6</v>
@@ -15413,10 +15369,10 @@
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B575" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C575" t="s">
         <v>6</v>
@@ -15432,14 +15388,14 @@
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A576" t="s">
-        <v>957</v>
+      <c r="A576" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="B576" t="s">
-        <v>499</v>
+        <v>1083</v>
       </c>
       <c r="C576" t="s">
-        <v>6</v>
+        <v>1087</v>
       </c>
       <c r="E576" t="s">
         <v>7</v>
@@ -15452,14 +15408,14 @@
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A577" s="1" t="s">
-        <v>1091</v>
+      <c r="A577" t="s">
+        <v>956</v>
       </c>
       <c r="B577" t="s">
-        <v>1085</v>
+        <v>501</v>
       </c>
       <c r="C577" t="s">
-        <v>1089</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>7</v>
@@ -15473,10 +15429,10 @@
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B578" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C578" t="s">
         <v>6</v>
@@ -15493,10 +15449,10 @@
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>959</v>
+        <v>904</v>
       </c>
       <c r="B579" t="s">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="C579" t="s">
         <v>6</v>
@@ -15513,10 +15469,10 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>906</v>
+        <v>958</v>
       </c>
       <c r="B580" t="s">
-        <v>14</v>
+        <v>504</v>
       </c>
       <c r="C580" t="s">
         <v>6</v>
@@ -15533,10 +15489,10 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B581" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C581" t="s">
         <v>6</v>
@@ -15553,10 +15509,10 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B582" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C582" t="s">
         <v>6</v>
@@ -15573,10 +15529,10 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B583" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C583" t="s">
         <v>6</v>
@@ -15593,10 +15549,10 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B584" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C584" t="s">
         <v>6</v>
@@ -15613,10 +15569,10 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B585" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="C585" t="s">
         <v>6</v>
@@ -15633,10 +15589,10 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B586" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C586" t="s">
         <v>6</v>
@@ -15653,10 +15609,10 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B587" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C587" t="s">
         <v>6</v>
@@ -15673,10 +15629,10 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B588" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C588" t="s">
         <v>6</v>
@@ -15693,10 +15649,10 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B589" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C589" t="s">
         <v>6</v>
@@ -15713,10 +15669,10 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B590" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C590" t="s">
         <v>6</v>
@@ -15733,10 +15689,10 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B591" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C591" t="s">
         <v>6</v>
@@ -15753,10 +15709,10 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B592" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C592" t="s">
         <v>6</v>
@@ -15773,10 +15729,10 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B593" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C593" t="s">
         <v>6</v>
@@ -15793,10 +15749,10 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B594" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C594" t="s">
         <v>6</v>
@@ -15813,10 +15769,10 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B595" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C595" t="s">
         <v>6</v>
@@ -15833,10 +15789,10 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B596" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C596" t="s">
         <v>6</v>
@@ -15853,10 +15809,10 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B597" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C597" t="s">
         <v>6</v>
@@ -15873,10 +15829,10 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B598" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C598" t="s">
         <v>6</v>
@@ -15893,10 +15849,10 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B599" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C599" t="s">
         <v>6</v>
@@ -15913,10 +15869,10 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B600" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C600" t="s">
         <v>6</v>
@@ -15933,10 +15889,10 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B601" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C601" t="s">
         <v>6</v>
@@ -15953,10 +15909,10 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B602" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C602" t="s">
         <v>6</v>
@@ -15973,10 +15929,10 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B603" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C603" t="s">
         <v>6</v>
@@ -15993,10 +15949,10 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B604" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C604" t="s">
         <v>6</v>
@@ -16013,10 +15969,10 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B605" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C605" t="s">
         <v>6</v>
@@ -16033,10 +15989,10 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B606" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C606" t="s">
         <v>6</v>
@@ -16053,10 +16009,10 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B607" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C607" t="s">
         <v>6</v>
@@ -16073,7 +16029,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B608" t="s">
         <v>553</v>
@@ -16093,7 +16049,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B609" t="s">
         <v>555</v>
@@ -16113,7 +16069,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B610" t="s">
         <v>556</v>
@@ -16133,7 +16089,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B611" t="s">
         <v>562</v>
@@ -16153,7 +16109,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B612" t="s">
         <v>563</v>
@@ -16173,7 +16129,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B613" t="s">
         <v>569</v>
@@ -16193,7 +16149,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B614" t="s">
         <v>568</v>
@@ -16213,7 +16169,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B615" t="s">
         <v>570</v>
@@ -16233,7 +16189,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B616" t="s">
         <v>572</v>
@@ -16253,7 +16209,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B617" t="s">
         <v>575</v>
@@ -16273,7 +16229,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B618" t="s">
         <v>576</v>
@@ -16293,7 +16249,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B619" t="s">
         <v>574</v>
@@ -16313,7 +16269,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B620" t="s">
         <v>579</v>
@@ -16333,7 +16289,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B621" t="s">
         <v>581</v>
@@ -16353,7 +16309,7 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B622" t="s">
         <v>580</v>
@@ -16373,7 +16329,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B623" t="s">
         <v>582</v>
@@ -16393,7 +16349,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B624" t="s">
         <v>583</v>
@@ -16413,7 +16369,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B625" t="s">
         <v>584</v>
@@ -16433,7 +16389,7 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B626" t="s">
         <v>585</v>
@@ -16453,7 +16409,7 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B627" t="s">
         <v>586</v>
@@ -16473,7 +16429,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B628" t="s">
         <v>589</v>
@@ -16493,7 +16449,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B629" t="s">
         <v>588</v>
@@ -16516,10 +16472,10 @@
         <v>770</v>
       </c>
       <c r="B630" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C630" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E630" t="s">
         <v>7</v>
@@ -16533,13 +16489,13 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B631" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C631" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E631" t="s">
         <v>7</v>
@@ -16553,13 +16509,13 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B632" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C632" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E632" t="s">
         <v>7</v>
@@ -16573,13 +16529,13 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B633" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C633" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E633" t="s">
         <v>7</v>
@@ -16593,13 +16549,13 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B634" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C634" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E634" t="s">
         <v>7</v>
@@ -16613,13 +16569,13 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B635" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C635" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E635" t="s">
         <v>7</v>
@@ -16633,13 +16589,13 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B636" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C636" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E636" t="s">
         <v>7</v>
@@ -16653,13 +16609,13 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B637" t="s">
+        <v>898</v>
+      </c>
+      <c r="C637" t="s">
         <v>900</v>
-      </c>
-      <c r="C637" t="s">
-        <v>902</v>
       </c>
       <c r="E637" t="s">
         <v>7</v>
@@ -16673,13 +16629,13 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B638" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C638" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E638" t="s">
         <v>7</v>
@@ -16693,13 +16649,13 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C639" t="s">
         <v>1017</v>
-      </c>
-      <c r="B639" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1019</v>
       </c>
       <c r="E639" t="s">
         <v>7</v>
@@ -16713,13 +16669,13 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B640" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C640" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E640" t="s">
         <v>7</v>
@@ -16733,13 +16689,13 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B641" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C641" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E641" t="s">
         <v>7</v>
@@ -16753,13 +16709,13 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B642" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C642" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E642" t="s">
         <v>7</v>
@@ -16773,13 +16729,13 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B643" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C643" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E643" t="s">
         <v>7</v>
@@ -16793,13 +16749,13 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B644" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C644" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E644" t="s">
         <v>7</v>
@@ -16813,13 +16769,13 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B645" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C645" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E645" t="s">
         <v>7</v>
@@ -16833,13 +16789,13 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B646" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C646" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E646" t="s">
         <v>7</v>
@@ -16853,13 +16809,13 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B647" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C647" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E647" t="s">
         <v>7</v>
@@ -16873,13 +16829,13 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B648" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C648" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E648" t="s">
         <v>7</v>
@@ -16893,16 +16849,16 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B649" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C649" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E649" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F649" t="s">
         <v>8</v>
@@ -16913,16 +16869,16 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B650" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C650" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E650" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F650" t="s">
         <v>8</v>
@@ -16933,16 +16889,16 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B651" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C651" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E651" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F651" t="s">
         <v>8</v>
@@ -16953,16 +16909,16 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B652" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C652" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E652" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F652" t="s">
         <v>8</v>
@@ -16973,16 +16929,16 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B653" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C653" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E653" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F653" t="s">
         <v>8</v>
@@ -16993,16 +16949,16 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B654" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C654" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E654" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F654" t="s">
         <v>8</v>
@@ -17013,16 +16969,16 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B655" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C655" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E655" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F655" t="s">
         <v>8</v>
@@ -17033,16 +16989,16 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B656" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C656" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E656" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F656" t="s">
         <v>8</v>
@@ -17053,16 +17009,16 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B657" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C657" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E657" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F657" t="s">
         <v>8</v>
@@ -17073,16 +17029,16 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B658" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C658" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E658" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F658" t="s">
         <v>8</v>
@@ -17093,16 +17049,16 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B659" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C659" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E659" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F659" t="s">
         <v>8</v>
@@ -17113,16 +17069,16 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B660" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C660" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E660" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F660" t="s">
         <v>8</v>
@@ -17133,16 +17089,16 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B661" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C661" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E661" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F661" t="s">
         <v>8</v>
@@ -17153,16 +17109,16 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B662" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C662" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E662" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F662" t="s">
         <v>8</v>
@@ -17173,16 +17129,16 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B663" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C663" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E663" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F663" t="s">
         <v>8</v>
@@ -17193,16 +17149,16 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B664" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C664" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E664" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F664" t="s">
         <v>8</v>
@@ -17213,16 +17169,16 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B665" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C665" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E665" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F665" t="s">
         <v>8</v>
@@ -17233,16 +17189,16 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B666" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C666" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E666" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F666" t="s">
         <v>8</v>
@@ -17253,16 +17209,16 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B667" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C667" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E667" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F667" t="s">
         <v>8</v>
@@ -17273,16 +17229,16 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B668" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C668" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E668" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F668" t="s">
         <v>8</v>
@@ -17293,16 +17249,16 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B669" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C669" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E669" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F669" t="s">
         <v>8</v>
@@ -17313,16 +17269,16 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B670" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C670" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E670" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F670" t="s">
         <v>8</v>
@@ -17333,16 +17289,16 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B671" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C671" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E671" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F671" t="s">
         <v>8</v>
@@ -17353,16 +17309,16 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B672" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C672" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E672" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F672" t="s">
         <v>8</v>
@@ -17373,16 +17329,16 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B673" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C673" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E673" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F673" t="s">
         <v>8</v>
@@ -17393,16 +17349,16 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B674" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C674" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E674" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F674" t="s">
         <v>8</v>
@@ -17413,16 +17369,16 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B675" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C675" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E675" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F675" t="s">
         <v>8</v>
@@ -17433,16 +17389,16 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B676" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C676" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E676" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F676" t="s">
         <v>8</v>
@@ -17453,16 +17409,16 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B677" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C677" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E677" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F677" t="s">
         <v>8</v>
@@ -17473,16 +17429,16 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B678" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C678" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E678" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F678" t="s">
         <v>8</v>
@@ -17493,16 +17449,16 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B679" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C679" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E679" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F679" t="s">
         <v>8</v>
@@ -17513,16 +17469,16 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B680" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C680" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E680" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F680" t="s">
         <v>8</v>
@@ -17533,16 +17489,16 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B681" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C681" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E681" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F681" t="s">
         <v>8</v>
@@ -17553,16 +17509,16 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B682" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C682" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E682" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F682" t="s">
         <v>8</v>
@@ -17573,16 +17529,16 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B683" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C683" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E683" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F683" t="s">
         <v>8</v>
@@ -17593,16 +17549,16 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B684" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C684" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E684" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F684" t="s">
         <v>8</v>
@@ -17613,16 +17569,16 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B685" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C685" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E685" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F685" t="s">
         <v>8</v>
@@ -17633,16 +17589,16 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B686" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C686" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E686" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F686" t="s">
         <v>8</v>
@@ -17653,16 +17609,16 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B687" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C687" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E687" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F687" t="s">
         <v>8</v>
@@ -17673,16 +17629,16 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B688" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C688" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E688" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F688" t="s">
         <v>8</v>
@@ -17693,16 +17649,16 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B689" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C689" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E689" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F689" t="s">
         <v>8</v>
@@ -17713,16 +17669,16 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B690" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C690" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E690" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F690" t="s">
         <v>8</v>
@@ -17733,16 +17689,16 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B691" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C691" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E691" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F691" t="s">
         <v>8</v>
@@ -17753,16 +17709,16 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B692" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C692" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E692" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F692" t="s">
         <v>8</v>
@@ -17773,16 +17729,16 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B693" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C693" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E693" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F693" t="s">
         <v>8</v>
@@ -17793,16 +17749,16 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B694" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C694" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E694" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F694" t="s">
         <v>8</v>
@@ -17813,16 +17769,16 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B695" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C695" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E695" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F695" t="s">
         <v>8</v>
@@ -17832,8 +17788,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A524:B629">
-    <sortCondition ref="A524:A629"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A523:B629">
+    <sortCondition ref="A523:A629"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
